--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484824_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484824_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.734500000000001</v>
+        <v>8.723699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9176</v>
+        <v>6.1712</v>
       </c>
       <c r="F2" t="n">
-        <v>2.817</v>
+        <v>2.5524</v>
       </c>
       <c r="G2" t="n">
         <v>2.6031</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1328</v>
+        <v>-0.1437</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8107</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.4133</v>
       </c>
       <c r="V2" t="n">
         <v>3.4338</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6441</v>
+        <v>5.0119</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0683</v>
+        <v>3.2246</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5758</v>
+        <v>1.7874</v>
       </c>
       <c r="G3" t="n">
         <v>2.7483</v>
@@ -688,13 +688,13 @@
         <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9911</v>
+        <v>-0.6233</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8107</v>
+        <v>-0.6545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1804</v>
+        <v>0.0312</v>
       </c>
       <c r="V3" t="n">
         <v>1.566</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6542</v>
+        <v>3.54</v>
       </c>
       <c r="E4" t="n">
-        <v>2.169</v>
+        <v>2.2664</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4852</v>
+        <v>1.2735</v>
       </c>
       <c r="G4" t="n">
         <v>1.5237</v>
@@ -766,13 +766,13 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>0.187</v>
+        <v>0.0728</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3281</v>
+        <v>-0.2306</v>
       </c>
       <c r="U4" t="n">
-        <v>0.515</v>
+        <v>0.3034</v>
       </c>
       <c r="V4" t="n">
         <v>0.6226</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7515</v>
+        <v>2.0257</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8774</v>
+        <v>1.0799</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1259</v>
+        <v>0.9458</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7831</v>
+        <v>0.1734</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5793</v>
+        <v>-1.4196</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2038</v>
+        <v>1.593</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1646</v>
+        <v>1.0676</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1819</v>
+        <v>-0.8499</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9828</v>
+        <v>1.9175</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3815</v>
+        <v>-0.8942</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6026</v>
+        <v>-0.5697</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7789</v>
+        <v>-0.3245</v>
       </c>
       <c r="P6" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9435</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-2.8305</v>
       </c>
       <c r="R6" t="n">
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3709</v>
+        <v>-0.3364</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0152</v>
+        <v>-0.2894</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3862</v>
+        <v>-0.047</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2828</v>
+        <v>1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>1.528</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6843</v>
+        <v>1.8619</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9237</v>
+        <v>2.6439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7606000000000001</v>
+        <v>-0.782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1734</v>
+        <v>2.7831</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4196</v>
+        <v>1.5793</v>
       </c>
       <c r="I7" t="n">
-        <v>1.593</v>
+        <v>1.2038</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0676</v>
+        <v>4.1646</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8499</v>
+        <v>2.1819</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9175</v>
+        <v>1.9828</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8942</v>
+        <v>-1.3815</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5697</v>
+        <v>-0.6026</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3245</v>
+        <v>-0.7789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6778</v>
+        <v>-0.2605</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4456</v>
+        <v>-0.2183</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2322</v>
+        <v>-0.0423</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0.2828</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>1.528</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4459</v>
+        <v>0.7235</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2106</v>
+        <v>0.1993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6565</v>
+        <v>0.5242</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6026</v>
@@ -1156,13 +1156,13 @@
         <v>3.3966</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7254</v>
+        <v>-0.4478</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1634</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.438</v>
+        <v>0.3057</v>
       </c>
       <c r="V9" t="n">
         <v>0.3208</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>I. CAMBRA DOBRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2299</v>
+        <v>0.1152</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4656</v>
+        <v>-0.0588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6955</v>
+        <v>0.174</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7976</v>
+        <v>0.2598</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4862</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3115</v>
+        <v>0.2598</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0446</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2091</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1645</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.753</v>
+        <v>0.2598</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.277</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.476</v>
+        <v>0.2598</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2934</v>
+        <v>-0.1446</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0436</v>
+        <v>-0.0588</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2498</v>
+        <v>-0.0858</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. CAMBRA DOBRE</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0888</v>
+        <v>0.0577</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0588</v>
+        <v>-0.7965</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1475</v>
+        <v>0.8542</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2598</v>
+        <v>-1.7976</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.4862</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2598</v>
+        <v>-0.3115</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.0446</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-1.2091</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.1645</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2598</v>
+        <v>-0.753</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2598</v>
+        <v>-0.476</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1711</v>
+        <v>-0.4656</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0588</v>
+        <v>-0.3745</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1123</v>
+        <v>-0.0911</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1941</v>
+        <v>-0.3747</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9772</v>
+        <v>-1.2107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7831</v>
+        <v>0.836</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1796</v>
@@ -1390,13 +1390,13 @@
         <v>2.8305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3545</v>
+        <v>-0.5351</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5262</v>
+        <v>-0.7597</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1717</v>
+        <v>0.2246</v>
       </c>
       <c r="V12" t="n">
         <v>-1.547</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5608</v>
+        <v>-0.5343</v>
       </c>
       <c r="E13" t="n">
         <v>-0.7083</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3897</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1711</v>
+        <v>-0.1446</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8313</v>
+        <v>-1.263</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8362</v>
+        <v>-3.7388</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0049</v>
+        <v>2.4758</v>
       </c>
       <c r="G14" t="n">
         <v>0.2864</v>
@@ -1546,13 +1546,13 @@
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09</v>
+        <v>-0.3417</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7055</v>
+        <v>-0.608</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7955</v>
+        <v>0.2664</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6415999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.8245</v>
+        <v>-2.4772</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.0312</v>
+        <v>-1.8162</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7933</v>
+        <v>-0.661</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9748</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6419</v>
+        <v>-0.2947</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6343</v>
+        <v>-0.4193</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0076</v>
+        <v>0.1247</v>
       </c>
       <c r="V15" t="n">
         <v>0.3018</v>
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>20.2751</v>
+        <v>20.863</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1207</v>
+        <v>10.7086</v>
       </c>
       <c r="F16" t="n">
-        <v>10.1544</v>
+        <v>10.1543</v>
       </c>
       <c r="G16" t="n">
-        <v>8.886100000000001</v>
+        <v>8.886099999999999</v>
       </c>
       <c r="H16" t="n">
         <v>9.101599999999999</v>
@@ -1702,10 +1702,10 @@
         <v>22.64400000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.253</v>
+        <v>-3.6652</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.570499999999999</v>
+        <v>-4.9824</v>
       </c>
       <c r="U16" t="n">
         <v>1.3173</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0649</v>
+        <v>3.0529</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1355</v>
+        <v>2.9407</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0706</v>
+        <v>0.1122</v>
       </c>
       <c r="G17" t="n">
         <v>2.0035</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5673</v>
+        <v>0.5552</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3092</v>
+        <v>0.1143</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2581</v>
+        <v>0.4409</v>
       </c>
       <c r="V17" t="n">
         <v>1.0603</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0221</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8783</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0.432</v>
@@ -1936,13 +1936,13 @@
         <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1822</v>
+        <v>0.2003</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2998</v>
+        <v>0.2205</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2066</v>
+        <v>0.3632</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2615</v>
+        <v>0.3231</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4681</v>
+        <v>0.0401</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7328</v>
@@ -2014,13 +2014,13 @@
         <v>2.4531</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8224</v>
+        <v>0.9791</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0676</v>
+        <v>-0.483</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8901</v>
+        <v>1.4621</v>
       </c>
       <c r="V20" t="n">
         <v>0.7395</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.117</v>
+        <v>0.2566</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3416</v>
+        <v>0.5365</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2246</v>
+        <v>-0.2799</v>
       </c>
       <c r="G21" t="n">
         <v>0.9483</v>
@@ -2092,13 +2092,13 @@
         <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3345</v>
+        <v>0.4741</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6872</v>
+        <v>0.632</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7319</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1601</v>
+        <v>-0.1902</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6982</v>
+        <v>-0.9905</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5382</v>
+        <v>0.8003</v>
       </c>
       <c r="G22" t="n">
         <v>1.4382</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1716</v>
+        <v>0.1415</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1205</v>
+        <v>-0.1718</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0512</v>
+        <v>0.3134</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8265</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9984</v>
+        <v>-0.9539</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5248</v>
+        <v>-0.4274</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4736</v>
+        <v>-0.5265</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2549</v>
@@ -2248,13 +2248,13 @@
         <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1999</v>
+        <v>0.2444</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4815</v>
+        <v>0.4286</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3208</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3433</v>
+        <v>-1.5238</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7431</v>
+        <v>0.3533</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0864</v>
+        <v>-1.8771</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8813</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9529</v>
+        <v>0.7724</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5719</v>
+        <v>0.1822</v>
       </c>
       <c r="U24" t="n">
-        <v>0.381</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6036</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7878</v>
+        <v>-3.0278</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3751</v>
+        <v>-2.7294</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4127</v>
+        <v>-0.2984</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4449</v>
+        <v>-0.9544</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.0208</v>
+        <v>-0.2833</v>
       </c>
       <c r="I25" t="n">
-        <v>1.576</v>
+        <v>-0.6711</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7996</v>
+        <v>-0.6073</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9235</v>
+        <v>0.0423</v>
       </c>
       <c r="L25" t="n">
-        <v>2.7231</v>
+        <v>-0.6496</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2445</v>
+        <v>-0.3471</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.0973</v>
+        <v>-0.3256</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1471</v>
+        <v>-0.0216</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.5853</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3179</v>
+        <v>-0.3186</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6183</v>
+        <v>-0.2352</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6996</v>
+        <v>-0.0835</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9244</v>
+        <v>-0.6226</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2636</v>
+        <v>-3.1956</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7294</v>
+        <v>-1.8623</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5341</v>
+        <v>-1.3333</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9544</v>
+        <v>-1.4449</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2833</v>
+        <v>-3.0208</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6711</v>
+        <v>1.576</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6073</v>
+        <v>1.7996</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0423</v>
+        <v>-0.9235</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6496</v>
+        <v>2.7231</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3471</v>
+        <v>-3.2445</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3256</v>
+        <v>-2.0973</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0216</v>
+        <v>-1.1471</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1322</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5543</v>
+        <v>0.9101</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2352</v>
+        <v>0.1312</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3192</v>
+        <v>0.7789</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6226</v>
+        <v>0.9244</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.2788</v>
+        <v>-5.2115</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.7138</v>
+        <v>-1.9086</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.5651</v>
+        <v>-3.3029</v>
       </c>
       <c r="G27" t="n">
         <v>-0.213</v>
@@ -2560,13 +2560,13 @@
         <v>0.9435</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4438</v>
+        <v>0.5111</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4514</v>
+        <v>0.2566</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0076</v>
+        <v>0.2546</v>
       </c>
       <c r="V27" t="n">
         <v>-2.4904</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.4948</v>
+        <v>-5.3746</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.844</v>
+        <v>-4.0389</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.6508</v>
+        <v>-1.3357</v>
       </c>
       <c r="G28" t="n">
         <v>-3.0427</v>
@@ -2638,13 +2638,13 @@
         <v>2.4531</v>
       </c>
       <c r="S28" t="n">
-        <v>0.114</v>
+        <v>0.2342</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1365</v>
+        <v>-0.3313</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2505</v>
+        <v>0.5656</v>
       </c>
       <c r="V28" t="n">
         <v>-1.2452</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.3243</v>
+        <v>-6.1768</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.337</v>
+        <v>-4.5576</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.9872</v>
+        <v>-1.6192</v>
       </c>
       <c r="G29" t="n">
         <v>-5.3686</v>
@@ -2716,13 +2716,13 @@
         <v>1.5096</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.2992</v>
+        <v>0.8482</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.1975</v>
+        <v>-0.4181</v>
       </c>
       <c r="U29" t="n">
-        <v>0.8983</v>
+        <v>1.2663</v>
       </c>
       <c r="V29" t="n">
         <v>-1.0903</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-20.2749</v>
+        <v>-18.9757</v>
       </c>
       <c r="E30" t="n">
-        <v>-10.1541</v>
+        <v>-10.1542</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.1205</v>
+        <v>-8.8215</v>
       </c>
       <c r="G30" t="n">
         <v>-8.8858</v>
@@ -2764,7 +2764,7 @@
         <v>-9.1014</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2156999999999998</v>
+        <v>0.2157000000000002</v>
       </c>
       <c r="J30" t="n">
         <v>10.4302</v>
@@ -2794,13 +2794,13 @@
         <v>13.209</v>
       </c>
       <c r="S30" t="n">
-        <v>4.253</v>
+        <v>5.552</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.3174</v>
+        <v>-1.3173</v>
       </c>
       <c r="U30" t="n">
-        <v>5.570499999999999</v>
+        <v>6.8696</v>
       </c>
       <c r="V30" t="n">
         <v>-6.2071</v>
